--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="85">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,201 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>AGUILA</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MILAGROS</t>
+  </si>
+  <si>
+    <t>MARITZA JULIANA</t>
+  </si>
+  <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>YEILI DAYNERIS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>JESUS</t>
   </si>
 </sst>
 </file>
@@ -529,16 +724,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -552,16 +750,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>48.48</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +864,7 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -686,7 +887,7 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -797,16 +998,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -820,16 +1024,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>48.48</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -869,6 +1076,581 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920190</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920191</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920193</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920199</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920200</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920201</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920280</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920206</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920208</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920290</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920209</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920210</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920212</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920213</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920217</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920322</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920366</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920367</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920375</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920382</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920396</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920196</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920198</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920215</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>19330051920374</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="123">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,63 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>ASCENCION</t>
   </si>
   <si>
@@ -88,6 +145,9 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -97,108 +157,183 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
     <t>ROBLES</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>TREJO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
+    <t>VILLA</t>
   </si>
   <si>
     <t>AGUILA</t>
   </si>
   <si>
+    <t>MILAGROS</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>MARITZA JULIANA</t>
+  </si>
+  <si>
+    <t>YEILI DAYNERIS</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
     <t>REYNA ARISBETH</t>
   </si>
   <si>
@@ -208,6 +343,12 @@
     <t>DULCE FERNANDA</t>
   </si>
   <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
     <t>FRIDA SOFIA</t>
   </si>
   <si>
@@ -217,58 +358,31 @@
     <t>YAMILET</t>
   </si>
   <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
     <t>LESLIE</t>
   </si>
   <si>
     <t>HEIDY MARIAM</t>
   </si>
   <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
     <t>JULIO CESAR</t>
   </si>
   <si>
     <t>INGRID SARAI</t>
   </si>
   <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
     <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -1046,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1078,16 +1192,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>19330051920280</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1101,16 +1215,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920191</v>
+        <v>20330051920202</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1124,16 +1238,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920193</v>
+        <v>20330051920206</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1147,16 +1261,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920199</v>
+        <v>20330051920209</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1170,16 +1284,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920200</v>
+        <v>20330051920213</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1193,16 +1307,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920201</v>
+        <v>20330051920217</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1216,22 +1330,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920280</v>
+        <v>20330051920270</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1239,22 +1353,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920206</v>
+        <v>20330051920271</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1262,22 +1376,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920208</v>
+        <v>20330051920276</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1285,22 +1399,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920290</v>
+        <v>20330051920279</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1308,22 +1422,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920209</v>
+        <v>20330051920321</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1331,22 +1445,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920210</v>
+        <v>20330051920322</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1354,22 +1468,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920212</v>
+        <v>20330051920323</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1377,22 +1491,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920213</v>
+        <v>20330051920324</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1400,22 +1514,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920217</v>
+        <v>20330051920325</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1423,16 +1537,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920322</v>
+        <v>20330051920326</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1446,22 +1560,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920366</v>
+        <v>20330051920327</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1469,22 +1583,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920367</v>
+        <v>20330051920330</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1492,22 +1606,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920375</v>
+        <v>20330051920333</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1515,22 +1629,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920382</v>
+        <v>20330051920335</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1538,16 +1652,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920396</v>
+        <v>19330051920366</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1561,85 +1675,85 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920196</v>
+        <v>19330051920367</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920198</v>
+        <v>19330051920375</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920215</v>
+        <v>19330051920382</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920374</v>
+        <v>19330051920396</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1648,6 +1762,420 @@
         <v>13</v>
       </c>
       <c r="G26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920190</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920191</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920193</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920196</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920198</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920199</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920200</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920201</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920208</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>113</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>19330051920290</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920210</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920212</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920215</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920269</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920272</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>20330051920273</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>19330051920238</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
+        <v>121</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>19330051920374</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -109,72 +109,72 @@
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>TREJO</t>
   </si>
   <si>
@@ -202,60 +202,60 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>AGUILA</t>
   </si>
   <si>
@@ -289,100 +289,100 @@
     <t>AXEL YAEL</t>
   </si>
   <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
     <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -1422,13 +1422,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
         <v>90</v>
@@ -1445,13 +1445,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920322</v>
+        <v>20330051920323</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
         <v>91</v>
@@ -1468,13 +1468,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
         <v>92</v>
@@ -1491,13 +1491,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
         <v>93</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
         <v>63</v>
@@ -1537,13 +1537,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
         <v>95</v>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
         <v>96</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920330</v>
+        <v>20330051920333</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
         <v>97</v>
@@ -1606,13 +1606,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
         <v>98</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920335</v>
+        <v>19330051920366</v>
       </c>
       <c r="B21" t="s">
         <v>35</v>
@@ -1641,10 +1641,10 @@
         <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1652,13 +1652,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920366</v>
+        <v>19330051920367</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
         <v>100</v>
@@ -1675,13 +1675,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920367</v>
+        <v>19330051920375</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
         <v>101</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920375</v>
+        <v>19330051920382</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920382</v>
+        <v>19330051920396</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
         <v>69</v>
@@ -1744,36 +1744,36 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920396</v>
+        <v>20330051920190</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
         <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920190</v>
+        <v>20330051920191</v>
       </c>
       <c r="B27" t="s">
         <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
         <v>105</v>
@@ -1790,13 +1790,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920191</v>
+        <v>20330051920193</v>
       </c>
       <c r="B28" t="s">
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
         <v>106</v>
@@ -1813,13 +1813,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920193</v>
+        <v>20330051920196</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
         <v>107</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920196</v>
+        <v>20330051920198</v>
       </c>
       <c r="B30" t="s">
         <v>42</v>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920198</v>
+        <v>20330051920199</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s">
         <v>73</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920199</v>
+        <v>20330051920200</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
@@ -1905,13 +1905,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920200</v>
+        <v>20330051920201</v>
       </c>
       <c r="B33" t="s">
         <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
         <v>111</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920201</v>
+        <v>20330051920208</v>
       </c>
       <c r="B34" t="s">
         <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
         <v>112</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920208</v>
+        <v>19330051920290</v>
       </c>
       <c r="B35" t="s">
         <v>46</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920290</v>
+        <v>20330051920210</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D36" t="s">
         <v>114</v>
@@ -1997,13 +1997,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920210</v>
+        <v>20330051920212</v>
       </c>
       <c r="B37" t="s">
         <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D37" t="s">
         <v>115</v>
@@ -2020,13 +2020,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920212</v>
+        <v>20330051920215</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="D38" t="s">
         <v>116</v>
@@ -2043,13 +2043,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920215</v>
+        <v>20330051920269</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
         <v>117</v>
@@ -2058,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2066,13 +2066,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>20330051920269</v>
+        <v>20330051920272</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
         <v>118</v>
@@ -2089,13 +2089,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>20330051920272</v>
+        <v>20330051920273</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
         <v>119</v>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>20330051920273</v>
+        <v>19330051920238</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
         <v>120</v>
@@ -2135,13 +2135,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920238</v>
+        <v>20330051920321</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="D43" t="s">
         <v>121</v>
@@ -2150,7 +2150,7 @@
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G43">
         <v>1</v>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="125">
   <si>
     <t>Mat</t>
   </si>
@@ -79,42 +79,93 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>MELENDEZ</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
     <t>PEÑA</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>GUTIERREZ</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
     <t>MAYA</t>
   </si>
   <si>
@@ -124,82 +175,76 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
   </si>
   <si>
     <t>TREJO</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
   </si>
   <si>
     <t>MEJIA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
   </si>
   <si>
     <t>LEON</t>
@@ -211,85 +256,115 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
     <t>AGUILA</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
     <t>MILAGROS</t>
   </si>
   <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
     <t>MARITZA JULIANA</t>
   </si>
   <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
     <t>YEILI DAYNERIS</t>
   </si>
   <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
     <t>SUSANA</t>
   </si>
   <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
     <t>LUIS DIEGO</t>
   </si>
   <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
   </si>
   <si>
     <t>JESUS SAMUEL</t>
@@ -314,75 +389,6 @@
   </si>
   <si>
     <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -1160,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1192,7 +1198,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920280</v>
+        <v>20330051920202</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -1201,7 +1207,7 @@
         <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1215,7 +1221,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920202</v>
+        <v>20330051920214</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1224,7 +1230,7 @@
         <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1238,22 +1244,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920206</v>
+        <v>20330051920270</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1261,22 +1267,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920209</v>
+        <v>20330051920271</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1284,22 +1290,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920213</v>
+        <v>20330051920276</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1307,22 +1313,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920217</v>
+        <v>20330051920279</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1330,22 +1336,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920270</v>
+        <v>20330051920322</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1353,7 +1359,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920271</v>
+        <v>19330051920366</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1362,13 +1368,13 @@
         <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1376,22 +1382,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920276</v>
+        <v>19330051920367</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1399,22 +1405,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920279</v>
+        <v>19330051920375</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1422,22 +1428,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920322</v>
+        <v>19330051920382</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1445,22 +1451,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920323</v>
+        <v>19330051920396</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
         <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1468,292 +1474,292 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920324</v>
+        <v>20330051920190</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920325</v>
+        <v>20330051920191</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
         <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920326</v>
+        <v>20330051920193</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920327</v>
+        <v>20330051920196</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920330</v>
+        <v>20330051920198</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
         <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920333</v>
+        <v>20330051920199</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920335</v>
+        <v>20330051920200</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920366</v>
+        <v>20330051920201</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920367</v>
+        <v>19330051920280</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920375</v>
+        <v>20330051920206</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920382</v>
+        <v>20330051920208</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920396</v>
+        <v>19330051920290</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
         <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920190</v>
+        <v>20330051920209</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1767,16 +1773,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920191</v>
+        <v>20330051920210</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1790,16 +1796,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920193</v>
+        <v>20330051920212</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1813,16 +1819,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920196</v>
+        <v>20330051920213</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1836,16 +1842,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920198</v>
+        <v>20330051920215</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1859,16 +1865,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920199</v>
+        <v>20330051920217</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
         <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -1882,22 +1888,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920200</v>
+        <v>20330051920269</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1905,22 +1911,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920201</v>
+        <v>20330051920272</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1928,22 +1934,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920208</v>
+        <v>20330051920273</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1951,22 +1957,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920290</v>
+        <v>19330051920238</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1974,22 +1980,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920210</v>
+        <v>20330051920321</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -1997,22 +2003,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920212</v>
+        <v>20330051920323</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2020,22 +2026,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920215</v>
+        <v>20330051920324</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D38" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2043,22 +2049,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920269</v>
+        <v>20330051920325</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
         <v>77</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2066,22 +2072,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>20330051920272</v>
+        <v>20330051920326</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2089,22 +2095,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>20330051920273</v>
+        <v>20330051920327</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2112,22 +2118,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920238</v>
+        <v>20330051920330</v>
       </c>
       <c r="B42" t="s">
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2135,16 +2141,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>20330051920321</v>
+        <v>20330051920333</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2158,24 +2164,47 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>19330051920374</v>
+        <v>20330051920335</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
         <v>79</v>
       </c>
       <c r="D44" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>19330051920374</v>
+      </c>
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" t="s">
         <v>9</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F45" t="s">
         <v>13</v>
       </c>
-      <c r="G44">
+      <c r="G45">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -91,10 +94,10 @@
     <t>OJEDA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ESTEVEZ</t>
@@ -109,15 +112,15 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>CRISTOBAL</t>
   </si>
   <si>
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -130,30 +133,33 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
     <t>BRUNO</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
     <t>ELIAS ALONSO</t>
   </si>
   <si>
@@ -166,10 +172,10 @@
     <t>KAREN YAZMIN</t>
   </si>
   <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
   </si>
   <si>
     <t>ERICK DE JESUS</t>
@@ -182,9 +188,6 @@
   </si>
   <si>
     <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
   </si>
   <si>
     <t>DANIELA</t>
@@ -1009,7 +1012,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920270</v>
+        <v>20330051920218</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -1018,13 +1021,13 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1032,7 +1035,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920271</v>
+        <v>20330051920270</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1041,7 +1044,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1055,7 +1058,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19220030050208</v>
+        <v>20330051920271</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1064,7 +1067,7 @@
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1078,7 +1081,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920276</v>
+        <v>19220030050208</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1087,7 +1090,7 @@
         <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1101,7 +1104,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920279</v>
+        <v>20330051920276</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1110,7 +1113,7 @@
         <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1124,7 +1127,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920322</v>
+        <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1133,7 +1136,7 @@
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1147,7 +1150,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920196</v>
+        <v>20330051920335</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1156,36 +1159,36 @@
         <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920273</v>
+        <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1193,22 +1196,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920321</v>
+        <v>20330051920273</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1216,16 +1219,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920331</v>
+        <v>20330051920321</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1239,16 +1242,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920335</v>
+        <v>20330051920331</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1268,10 +1271,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1291,10 +1294,10 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -82,6 +82,15 @@
     <t>DE LA TEJA</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -91,21 +100,12 @@
     <t>DE LUNA</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>OJEDA</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>COCOTLE</t>
   </si>
   <si>
@@ -121,6 +121,15 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -130,21 +139,12 @@
     <t>CORDOVA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
@@ -160,6 +160,15 @@
     <t>ALISSON FERNANDA</t>
   </si>
   <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
     <t>ELIAS ALONSO</t>
   </si>
   <si>
@@ -169,19 +178,10 @@
     <t>EUDY</t>
   </si>
   <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
     <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
   </si>
   <si>
     <t>SURISADAY</t>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920270</v>
+        <v>20330051920329</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1050,7 +1050,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920271</v>
+        <v>20330051920335</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1073,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19220030050208</v>
+        <v>20330051920196</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1096,15 +1096,15 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920276</v>
+        <v>20330051920270</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1122,12 +1122,12 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920329</v>
+        <v>20330051920271</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1142,15 +1142,15 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920335</v>
+        <v>19220030050208</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1165,15 +1165,15 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920196</v>
+        <v>20330051920273</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1188,7 +1188,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920273</v>
+        <v>20330051920276</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,12 @@
     <t>DE LA TEJA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -121,6 +127,12 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -158,6 +170,12 @@
   </si>
   <si>
     <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
   </si>
   <si>
     <t>JUAN GUILLERMO</t>
@@ -980,7 +998,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1018,10 +1036,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1035,22 +1053,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920329</v>
+        <v>20330051920267</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1058,16 +1076,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920335</v>
+        <v>20330051920397</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1081,68 +1099,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920196</v>
+        <v>20330051920329</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920270</v>
+        <v>20330051920335</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920271</v>
+        <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1150,16 +1168,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19220030050208</v>
+        <v>20330051920270</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1173,16 +1191,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920273</v>
+        <v>20330051920271</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1196,16 +1214,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920276</v>
+        <v>19220030050208</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1219,22 +1237,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920321</v>
+        <v>20330051920273</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1242,22 +1260,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920331</v>
+        <v>20330051920276</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1265,22 +1283,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920366</v>
+        <v>20330051920321</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1288,24 +1306,70 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920382</v>
+        <v>20330051920331</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920366</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
         <v>9</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>13</v>
       </c>
-      <c r="G14">
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920382</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="74">
   <si>
     <t>Mat</t>
   </si>
@@ -82,42 +82,54 @@
     <t>DE LA TEJA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>CRISTOBAL</t>
   </si>
   <si>
@@ -127,42 +139,45 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>BRUNO</t>
   </si>
   <si>
@@ -172,40 +187,52 @@
     <t>ALISSON FERNANDA</t>
   </si>
   <si>
-    <t>VALERIA</t>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
   </si>
   <si>
     <t>EMMANUEL</t>
   </si>
   <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
     <t>JUAN GUILLERMO</t>
   </si>
   <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
     <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
   </si>
   <si>
     <t>DANIELA</t>
@@ -998,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1036,10 +1063,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1053,16 +1080,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920267</v>
+        <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1076,22 +1103,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920397</v>
+        <v>20330051920274</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1099,22 +1126,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920329</v>
+        <v>20330051920279</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1122,16 +1149,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920335</v>
+        <v>20330051920320</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1145,68 +1172,68 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920196</v>
+        <v>20330051920322</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920270</v>
+        <v>20330051920397</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920271</v>
+        <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1214,16 +1241,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19220030050208</v>
+        <v>20330051920270</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1237,16 +1264,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920273</v>
+        <v>20330051920271</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1260,16 +1287,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920276</v>
+        <v>19220030050208</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1283,22 +1310,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920321</v>
+        <v>20330051920273</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1306,22 +1333,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920331</v>
+        <v>20330051920276</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1329,22 +1356,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920366</v>
+        <v>20330051920321</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1352,24 +1379,116 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920382</v>
+        <v>20330051920329</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920331</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920335</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920366</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
         <v>9</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F19" t="s">
         <v>13</v>
       </c>
-      <c r="G16">
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920382</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
   <si>
     <t>Mat</t>
   </si>
@@ -79,166 +79,112 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>DE LA TEJA</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>LARA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
   </si>
   <si>
     <t>ALISSON FERNANDA</t>
   </si>
   <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
     <t>DANIEL ELEAZAR</t>
   </si>
   <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
     <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
     <t>SURISADAY</t>
   </si>
   <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
   </si>
 </sst>
 </file>
@@ -665,10 +611,10 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -677,7 +623,7 @@
         <v>35</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -691,16 +637,16 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>63.16</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H4">
         <v>6.4</v>
@@ -782,19 +728,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>79.31</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -808,10 +754,10 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -820,7 +766,7 @@
         <v>35</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -834,16 +780,16 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>57.89</v>
+        <v>68.42</v>
       </c>
       <c r="H4">
         <v>6.4</v>
@@ -860,19 +806,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -928,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>86.20999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H2">
         <v>6.8</v>
@@ -951,19 +897,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -977,19 +923,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>57.89</v>
+        <v>78.95</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1006,16 +952,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>69.7</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1025,7 +971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1057,16 +1003,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920218</v>
+        <v>20330051920204</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1080,22 +1026,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920314</v>
+        <v>20330051920218</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1103,16 +1049,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920274</v>
+        <v>20330051920279</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1126,114 +1072,114 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920279</v>
+        <v>20330051920196</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920320</v>
+        <v>19330051920314</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920322</v>
+        <v>20330051920270</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920397</v>
+        <v>20330051920272</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920196</v>
+        <v>20330051920274</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1241,22 +1187,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920270</v>
+        <v>20330051920320</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1264,22 +1210,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920271</v>
+        <v>20330051920321</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1287,22 +1233,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19220030050208</v>
+        <v>20330051920327</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1310,22 +1256,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920273</v>
+        <v>19330051920358</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1333,162 +1279,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920276</v>
+        <v>19330051920369</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920321</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920329</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920331</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920335</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920366</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920382</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>
